--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260909.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260909.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.38%</t>
+          <t>10.25%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>8.95%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.65%</t>
+          <t>8.41%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,949,000</t>
+          <t>20,300,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>7.07%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,300,000</t>
+          <t>5,949,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.86%</t>
+          <t>7.05%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.29%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.01%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>4.95%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>4.94%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>7,240,000</t>
+          <t>6,464,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.57%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>6,464,000</t>
+          <t>7,240,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.55%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.42%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.77%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.67%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>207,900</t>
+          <t>1,731,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,731,000</t>
+          <t>207,900</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>5,231,264,000</t>
+          <t>6,098,736,338</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2,008,358,738</t>
+          <t>2,038,642,138</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-972,861,199</t>
+          <t>-1,664,304,374</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,660,081,297</t>
+          <t>1,484,081,297</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
